--- a/public/templates/examples/A-044-DataRetentionSchedule-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-044-DataRetentionSchedule-EXAMPLE-L.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -216,12 +216,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -335,7 +335,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -369,7 +369,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-044-DataRetentionSchedule-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-044-DataRetentionSchedule-EXAMPLE-L.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Aptos"/>
@@ -105,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -136,6 +138,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,7 +585,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -725,7 +731,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Data Category</t>
@@ -767,7 +773,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="50.5" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>9-1-1 call audio recordings</t>
@@ -803,13 +809,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="H15" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="16" ht="50.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>CAD incident records</t>
@@ -845,13 +849,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+      <c r="H16" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="17" ht="50.5" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Text-to-9-1-1 / RTT transcripts</t>
@@ -887,13 +889,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="H17" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="18" ht="50.5" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>ALI / location query logs</t>
@@ -929,13 +929,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+      <c r="H18" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="19" ht="50.5" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Radio / console event logs</t>
@@ -971,13 +969,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+      <c r="H19" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>IDACS / CJIS query logs</t>
@@ -1013,13 +1009,11 @@
           <t>IDACS TAC</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="H20" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="21" ht="50.5" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Comms-room video (CCTV)</t>
@@ -1055,13 +1049,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+      <c r="H21" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="22" ht="50.5" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Cybersecurity / incident logs</t>
@@ -1097,13 +1089,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+      <c r="H22" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="23" ht="66.4" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Personnel training &amp; screening records</t>
@@ -1139,13 +1129,11 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+      <c r="H23" s="12">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="24" ht="50.5" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Policies &amp; administrative records</t>
@@ -1181,10 +1169,8 @@
           <t>Records Custodian</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
+      <c r="H24" s="12">
+        <v>46388</v>
       </c>
     </row>
     <row r="26">
@@ -1316,10 +1302,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D40" s="13">
+        <v>46174</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -1338,10 +1322,8 @@
           <t>Dr. Lisa Park</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D41" s="13">
+        <v>46174</v>
       </c>
     </row>
     <row r="43">
@@ -1373,16 +1355,14 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="34.7" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="B45" s="12">
+        <v>46174</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -1427,7 +1407,8 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>